--- a/order_management/24.4-sorting/24.4 - Sorting.xlsx
+++ b/order_management/24.4-sorting/24.4 - Sorting.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Endpoints" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Open Questions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Cross-Epic Dependencies" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Implementation Status" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Requirements'!$A$1:$K$4</definedName>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -139,6 +140,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -643,6 +648,54 @@
       </c>
       <c r="B13" s="8" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Implementation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Not started — analysis only</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Impl Branch</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Impl Commits</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -656,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -670,6 +723,7 @@
     <col width="48" customWidth="1" min="9" max="9"/>
     <col width="62" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,6 +782,11 @@
           <t>Confluence</t>
         </is>
       </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Impl Status (2026-07-01)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -781,6 +840,11 @@
           <t>Open §Order Management → Story 24.4</t>
         </is>
       </c>
+      <c r="L2" s="11" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -834,6 +898,11 @@
           <t>Open §Order Management → Story 24.4</t>
         </is>
       </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -885,6 +954,11 @@
       <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Open §Order Management → Story 24.4</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>◻ Not started</t>
         </is>
       </c>
     </row>
@@ -980,11 +1054,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -998,6 +1074,16 @@
           <t>Open Question</t>
         </is>
       </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Resolution / Decision</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1008,6 +1094,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>None — all ambiguities resolved against code/spec.</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>No open questions — all ambiguities resolved against code/spec.</t>
         </is>
       </c>
     </row>
@@ -1059,4 +1155,118 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>Not started — analysis/feasibility stage only. No branch, no SBE ticket, no PR, no Swagger tag. Extended tracking format applied; per-requirement build status is ◻ Not started.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Remaining — 24.4-a</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>◻ Not started. Sort by Order column (order_number) asc/desc via sortBy/sortOrder query params → Prisma orderBy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Remaining — 24.4-b</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>◻ Not started. Sort by Date column (created_at) asc/desc via sortBy/sortOrder query params → Prisma orderBy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Remaining — 24.4-c</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>◻ Not started. Backend full-dataset sort — orderBy applied before skip/take pagination so ordering spans the entire result set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Open decision</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>None — all ambiguities resolved against code/spec. No code is blocked on a team decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Dependency — 24.1</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Shared list endpoint GET /api/v1/orders owned by story 24.1; 24.4 layers sortBy/sortOrder query params onto it (no separate route).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Out of API scope</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Front-end sort-control wiring. Nothing in this story is marked Out of Scope.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/order_management/24.4-sorting/24.4 - Sorting.xlsx
+++ b/order_management/24.4-sorting/24.4 - Sorting.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Shared list endpoint with optional sortBy (order_number | created_at) and sortOrder (asc | desc) translated to a Prisma orderBy applied across the full dataset before pagination.</t>
+          <t>Shared list endpoint with sort_by (enum: order_number | created_at, default created_at) and sort_order (enum: asc | desc, default desc) query params — snake_case to match sibling ppl-order — mapped 1:1 to Prisma orderBy: { [sort_by]: sort_order }, applied across the full dataset before skip/take pagination.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>◻ Not started. Sort by Order column (order_number) asc/desc via sortBy/sortOrder query params → Prisma orderBy.</t>
+          <t>◻ Not started. Sort by Order column (order_number) asc/desc via sort_by=order_number + sort_order query params → Prisma orderBy.</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>◻ Not started. Sort by Date column (created_at) asc/desc via sortBy/sortOrder query params → Prisma orderBy.</t>
+          <t>◻ Not started. Sort by Date column (created_at) asc/desc via sort_by=created_at (default) + sort_order (default desc) query params → Prisma orderBy.</t>
         </is>
       </c>
     </row>

--- a/order_management/24.4-sorting/24.4 - Sorting.xlsx
+++ b/order_management/24.4-sorting/24.4 - Sorting.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,12 @@
       <color rgb="000563C1"/>
       <u val="single"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +85,13 @@
         <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,11 +113,25 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -144,6 +167,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -658,7 +690,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Not started — analysis only</t>
+          <t>All 3 reqs shipped in SBE-1125 (GET /api/v1/orders sorting)</t>
         </is>
       </c>
     </row>
@@ -670,7 +702,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SBE-1125 (admin-backend-api)</t>
         </is>
       </c>
     </row>
@@ -682,7 +714,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6dc3104 (feat — OM list endpoint), b95627b (SonarQube S7781 fix)</t>
         </is>
       </c>
     </row>
@@ -694,7 +726,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bitbucket #513 → dev</t>
         </is>
       </c>
     </row>
@@ -784,7 +816,7 @@
       </c>
       <c r="L1" s="9" t="inlineStr">
         <is>
-          <t>Impl Status (2026-07-01)</t>
+          <t>Impl Status (2026-07-02)</t>
         </is>
       </c>
     </row>
@@ -840,9 +872,9 @@
           <t>Open §Order Management → Story 24.4</t>
         </is>
       </c>
-      <c r="L2" s="11" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L2" s="13" t="inlineStr">
+        <is>
+          <t>✅ Done — sort_by=order_number + sort_order → Prisma orderBy.</t>
         </is>
       </c>
     </row>
@@ -898,9 +930,9 @@
           <t>Open §Order Management → Story 24.4</t>
         </is>
       </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L3" s="13" t="inlineStr">
+        <is>
+          <t>✅ Done — sort_by=created_at (default) + sort_order (default desc) → Prisma orderBy.</t>
         </is>
       </c>
     </row>
@@ -956,9 +988,9 @@
           <t>Open §Order Management → Story 24.4</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>◻ Not started</t>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>✅ Done — orderBy applied before skip/take (full-dataset); id tiebreaker for stable paging.</t>
         </is>
       </c>
     </row>
@@ -1163,106 +1195,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Detail</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
-        <is>
-          <t>Not started — analysis/feasibility stage only. No branch, no SBE ticket, no PR, no Swagger tag. Extended tracking format applied; per-requirement build status is ◻ Not started.</t>
+      <c r="B2" s="15" t="inlineStr">
+        <is>
+          <t>Shipped — built, live-smoke-tested, code-reviewed; all gates green; PR open against dev (not yet merged).</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Remaining — 24.4-a</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>◻ Not started. Sort by Order column (order_number) asc/desc via sort_by=order_number + sort_order query params → Prisma orderBy.</t>
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>SBE-1125 (admin-backend-api)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Remaining — 24.4-b</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>◻ Not started. Sort by Date column (created_at) asc/desc via sort_by=created_at (default) + sort_order (default desc) query params → Prisma orderBy.</t>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>SBE ticket</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>SBE-1125</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Remaining — 24.4-c</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>◻ Not started. Backend full-dataset sort — orderBy applied before skip/take pagination so ordering spans the entire result set.</t>
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>Commits</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>6dc3104 (feat — OM list endpoint), b95627b (SonarQube S7781 fix)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Open decision</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>None — all ambiguities resolved against code/spec. No code is blocked on a team decision.</t>
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>Bitbucket #513 → dev</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>Dependency — 24.1</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>Shared list endpoint GET /api/v1/orders owned by story 24.1; 24.4 layers sortBy/sortOrder query params onto it (no separate route).</t>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>Swagger tag</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>Admin - Order Management (/api/docs/admin)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Build gates</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Pipeline #838 SUCCESSFUL — gitleaks + lint/typecheck/test (2702 pass; orders module 48) + SonarQube quality gate all green</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>Live smoke</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Paged one row at a time over orders sharing created_at — no duplicates, complete coverage, stable order (id tiebreaker) — passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Confirmed build scope</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>GET /api/v1/orders?sort_by&amp;sort_order — 24.4-a,b,c shipped (all 3). sort_by=order_number|created_at (default created_at) + sort_order asc|desc (default desc) → Prisma orderBy with id tiebreaker; applied before skip/take (full-dataset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>Remaining</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>None — all 3 requirements shipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Out of API scope</t>
         </is>
       </c>
-      <c r="B8" s="11" t="inlineStr">
-        <is>
-          <t>Front-end sort-control wiring. Nothing in this story is marked Out of Scope.</t>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Front-end sort-control wiring.</t>
         </is>
       </c>
     </row>
